--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3">
         <v>14</v>
       </c>
       <c r="G3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H3">
         <v>426</v>
